--- a/350-MiseAJourJDVJ264/ig/StructureDefinition-esms-bundle-resultat-recherche-decision-evaluation.xlsx
+++ b/350-MiseAJourJDVJ264/ig/StructureDefinition-esms-bundle-resultat-recherche-decision-evaluation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:38:47+00:00</t>
+    <t>2026-06-24T13:06:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/350-MiseAJourJDVJ264/ig/StructureDefinition-esms-bundle-resultat-recherche-decision-evaluation.xlsx
+++ b/350-MiseAJourJDVJ264/ig/StructureDefinition-esms-bundle-resultat-recherche-decision-evaluation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:06:28+00:00</t>
+    <t>2026-06-24T14:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/350-MiseAJourJDVJ264/ig/StructureDefinition-esms-bundle-resultat-recherche-decision-evaluation.xlsx
+++ b/350-MiseAJourJDVJ264/ig/StructureDefinition-esms-bundle-resultat-recherche-decision-evaluation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T14:06:33+00:00</t>
+    <t>2026-06-26T14:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
